--- a/Europe_summary.xlsx
+++ b/Europe_summary.xlsx
@@ -578,7 +578,7 @@
         <v>1447493</v>
       </c>
       <c r="G6" t="n">
-        <v>1446</v>
+        <v>1446425</v>
       </c>
       <c r="H6" t="n">
         <v>1447320</v>
@@ -604,7 +604,7 @@
         <v>1738908</v>
       </c>
       <c r="G7" t="n">
-        <v>1741</v>
+        <v>1740569</v>
       </c>
       <c r="H7" t="n">
         <v>1739960</v>
@@ -630,7 +630,7 @@
         <v>2145942</v>
       </c>
       <c r="G8" t="n">
-        <v>1823</v>
+        <v>1822632</v>
       </c>
       <c r="H8" t="n">
         <v>1832170</v>
@@ -1370,7 +1370,7 @@
         <v>694026961</v>
       </c>
       <c r="G42" t="n">
-        <v>167034</v>
+        <v>167033674</v>
       </c>
       <c r="H42" t="n">
         <v>162243534</v>
@@ -1396,7 +1396,7 @@
         <v>740738278</v>
       </c>
       <c r="G43" t="n">
-        <v>177813</v>
+        <v>177813277</v>
       </c>
       <c r="H43" t="n">
         <v>177097530</v>
@@ -1422,7 +1422,7 @@
         <v>625028160</v>
       </c>
       <c r="G44" t="n">
-        <v>202703</v>
+        <v>202702558</v>
       </c>
       <c r="H44" t="n">
         <v>203839780</v>
@@ -1466,7 +1466,7 @@
         <v>155082428</v>
       </c>
       <c r="G46" t="n">
-        <v>38484</v>
+        <v>38483582</v>
       </c>
       <c r="H46" t="n">
         <v>38770609</v>
@@ -1492,7 +1492,7 @@
         <v>213208583</v>
       </c>
       <c r="G47" t="n">
-        <v>54304</v>
+        <v>54304484</v>
       </c>
       <c r="H47" t="n">
         <v>53302146</v>
@@ -1518,7 +1518,7 @@
         <v>237492372</v>
       </c>
       <c r="G48" t="n">
-        <v>61035</v>
+        <v>61035487</v>
       </c>
       <c r="H48" t="n">
         <v>59373100</v>
@@ -2000,7 +2000,7 @@
         <v>246230687</v>
       </c>
       <c r="G71" t="n">
-        <v>105763</v>
+        <v>105762552</v>
       </c>
       <c r="H71" t="n">
         <v>106793430</v>
@@ -2026,7 +2026,7 @@
         <v>227145371</v>
       </c>
       <c r="G72" t="n">
-        <v>109913</v>
+        <v>109912830</v>
       </c>
       <c r="H72" t="n">
         <v>110689319</v>
@@ -2052,7 +2052,7 @@
         <v>236842499</v>
       </c>
       <c r="G73" t="n">
-        <v>118679</v>
+        <v>118679120</v>
       </c>
       <c r="H73" t="n">
         <v>116711880</v>
@@ -2300,7 +2300,7 @@
         <v>143440009</v>
       </c>
       <c r="G85" t="n">
-        <v>36588</v>
+        <v>36587679</v>
       </c>
       <c r="H85" t="n">
         <v>35860002</v>
@@ -2326,7 +2326,7 @@
         <v>164806847</v>
       </c>
       <c r="G86" t="n">
-        <v>36066</v>
+        <v>36065959</v>
       </c>
       <c r="H86" t="n">
         <v>41201711</v>
@@ -2352,7 +2352,7 @@
         <v>191910568</v>
       </c>
       <c r="G87" t="n">
-        <v>37294</v>
+        <v>37294481</v>
       </c>
       <c r="H87" t="n">
         <v>47977660</v>
